--- a/artfynd/A 28395-2024 artfynd.xlsx
+++ b/artfynd/A 28395-2024 artfynd.xlsx
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79740481</v>
+        <v>92005884</v>
       </c>
       <c r="B2" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Frogetorp, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561497.0072684396</v>
+        <v>561493</v>
       </c>
       <c r="R2" t="n">
-        <v>6521054.762216154</v>
+        <v>6521098</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,75 +762,64 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sarah J Leander</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sarah J Leander</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Vesa Jussila</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92005884</v>
+        <v>79740481</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+          <t>Frogetorp, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561493.2034906608</v>
+        <v>561497</v>
       </c>
       <c r="R3" t="n">
-        <v>6521098.202860254</v>
+        <v>6521055</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,22 +863,23 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Sarah J Leander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Vesa Jussila</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Holmen</t>
-        </is>
-      </c>
+          <t>Sarah J Leander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28395-2024 artfynd.xlsx
+++ b/artfynd/A 28395-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005884</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79740481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>